--- a/AAII_Financials/Quarterly/TKGBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TKGBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="92">
   <si>
     <t>TKGBY</t>
   </si>
@@ -656,89 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -748,8 +748,11 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -792,15 +795,15 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>1946000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3215100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,8 +813,11 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -872,8 +878,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,8 +970,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1020,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1082,8 +1098,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1126,8 +1145,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1144,8 +1163,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1188,15 +1210,15 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
         <v>-28800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-54900</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1206,8 +1228,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,8 +1252,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1271,15 +1297,15 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>1244300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2349200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1289,8 +1315,11 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1333,15 +1362,15 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>701700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>865900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,8 +1407,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1419,15 +1452,15 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-90400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-461100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,8 +1470,11 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1481,15 +1517,15 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>640100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>459700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,8 +1535,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1543,8 +1582,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1561,8 +1600,11 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1605,15 +1647,15 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>611300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>404800</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1623,8 +1665,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1667,15 +1712,15 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>532300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>406000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1685,8 +1730,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1747,8 +1795,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1791,15 +1842,15 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>79100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,8 +1860,11 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1853,15 +1907,15 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
         <v>78700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4500</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1871,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1977,8 +2037,8 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -1995,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2057,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2119,8 +2185,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2163,15 +2232,15 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>90400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>461100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,8 +2250,11 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2225,15 +2297,15 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
         <v>78700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4500</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2243,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,8 +2380,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2349,15 +2427,15 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
         <v>78700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4500</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,64 +2445,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,53 +2567,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13132100</v>
+      </c>
+      <c r="E41" s="3">
         <v>10975800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13376200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11912400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11233100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13276100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9343000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11329700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10632700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14298400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11791200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13117200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12880600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12411000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,53 +2630,56 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4399800</v>
+      </c>
+      <c r="E42" s="3">
         <v>3129700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3121100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5131600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5310400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3188100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2714200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4632400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4922100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4040600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3868000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2861100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3003100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3325600</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,53 +2695,56 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1440200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1259900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1336900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1325900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1249600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>724500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1269100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1127200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>695800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>650800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>685500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>586000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>487500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>712900</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -2668,8 +2760,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2712,8 +2807,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2730,53 +2825,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>343900</v>
+      </c>
+      <c r="E45" s="3">
         <v>258100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>241500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>216100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>188700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>181500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>198400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>178100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>165800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>150400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>165800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>189900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>115900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>168900</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -2792,53 +2890,56 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30622800</v>
+      </c>
+      <c r="E46" s="3">
         <v>25287000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29296300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29775800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28713700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26591600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22388200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26576900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24739400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22581600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21928500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21631000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21380200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22048700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -2854,53 +2955,56 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7888300</v>
+      </c>
+      <c r="E47" s="3">
         <v>10284100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8893600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6716700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5753600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8741900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8159300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6203200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5140400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3688100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5205500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3659900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2671300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3223200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2916,53 +3020,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1084700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1183300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1191000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1029200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1063800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1036800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1037000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>822500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>848800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>699900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>742400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>639500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>646400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>724800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,53 +3085,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>192400</v>
+      </c>
+      <c r="E49" s="3">
         <v>176600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>181700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>175300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>165600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>141800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>123400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>106300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>98200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>88200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>86200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>62700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>59300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>71500</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -3040,8 +3150,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3102,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3164,53 +3280,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7249100</v>
+      </c>
+      <c r="E52" s="3">
         <v>7865500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2629300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3144900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3058800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2937700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2692300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2204100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3216500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5719300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4947300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6108500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9205600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7372800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,8 +3345,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3288,53 +3410,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>111803000</v>
+      </c>
+      <c r="E54" s="3">
         <v>107549100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>105850300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>101173100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95997500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>92202200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84893200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>84163000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>79872800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76016400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74453600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>72100000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>72546600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>76681900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,53 +3527,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74288700</v>
+      </c>
+      <c r="E57" s="3">
         <v>71196600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>73317600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>70127300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67320200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>68122300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>60910800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>60205400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56578800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>54144000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>54272700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>52431800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>53737000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>54184400</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -3460,53 +3590,56 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3571100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2592100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3200100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4622200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4919900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2243600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2560300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4490000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4796000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3565600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>800300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2937900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2952700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3082600</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -3522,53 +3655,56 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10560600</v>
+      </c>
+      <c r="E59" s="3">
         <v>10618700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5982000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5566500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5161100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4426600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4827500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4251300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3551200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3535600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3050000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2746400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2173800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3311900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,53 +3720,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>88502700</v>
+      </c>
+      <c r="E60" s="3">
         <v>84487100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82584600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>80416600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>77462700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74835500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68341400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>68989800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64967500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>61280500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>58155000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>58148000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>58892300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>60611100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -3646,53 +3785,56 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10827000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10327700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10733700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8937500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7252300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6219100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5511100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4711800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4771100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4918300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6440000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4482800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4519900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4888400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3708,53 +3850,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1722000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2260800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1841800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1667500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1534000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1929800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1435200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1385700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1388100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1741400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1382400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1487000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1766300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1891500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3770,8 +3915,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3832,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3894,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3956,53 +4110,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>101313300</v>
+      </c>
+      <c r="E66" s="3">
         <v>97362700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>95454800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91255700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86474200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83223400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75523200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>75272400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>71318900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>68112100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>66147600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64242000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65314000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>67593800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4018,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4104,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4228,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4290,53 +4460,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8842800</v>
+      </c>
+      <c r="E72" s="3">
         <v>8593000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8634400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8285700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7886600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7538900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7894300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7434800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7081300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6488600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6795800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6267500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5683700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7220000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4352,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4414,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4476,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4538,53 +4720,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10430400</v>
+      </c>
+      <c r="E76" s="3">
         <v>10136000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10335900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9865300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9478700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8942100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9324200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8850800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8520200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7877600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8274900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7830600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7209000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9063500</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4600,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4662,64 +4850,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4729,8 +4920,11 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4773,15 +4967,15 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
         <v>78700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4500</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,53 +5012,54 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E83" s="3">
         <v>24800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>20800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14500</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -4877,8 +5075,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4939,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5001,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5063,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5125,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5187,59 +5400,62 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3612700</v>
+      </c>
+      <c r="E89" s="3">
         <v>588400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6715200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5970000</v>
       </c>
-      <c r="G89" s="3">
-        <v>-6078000</v>
-      </c>
       <c r="H89" s="3">
+        <v>-6023500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-5762600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5374900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6422200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4451100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4516000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4769300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1386400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8407300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2993500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5748200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>970300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,53 +5492,54 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>10200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-39600</v>
-      </c>
       <c r="H91" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-131100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-127900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-51200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-50200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-53000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-75800</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -5335,8 +5555,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5397,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5459,59 +5685,62 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1935900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2316500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-50700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-716400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-115300</v>
-      </c>
       <c r="H94" s="3">
+        <v>-142400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-670000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>117500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>28000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-470100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1128400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-638800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-718000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-316400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1820700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-334800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-322600</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5521,8 +5750,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,59 +5777,60 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>474100</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>267400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>205300</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>242000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>159600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>336700</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R96" s="3">
         <v>-58600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-22300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -5607,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5669,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5731,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5793,59 +6035,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6251300</v>
+      </c>
+      <c r="E100" s="3">
         <v>507300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8374800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6361400</v>
       </c>
-      <c r="G100" s="3">
-        <v>3629500</v>
-      </c>
       <c r="H100" s="3">
+        <v>3668600</v>
+      </c>
+      <c r="I100" s="3">
         <v>11914100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4403100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6520500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4101600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4266300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5725300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3334300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>10485900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6426300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1622400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>878000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,59 +6100,62 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E101" s="3">
         <v>170700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-31600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>93600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>155300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>95700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-373000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1078300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>168900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-58000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>216700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>234900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>270200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4428000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2855000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5917,59 +6165,62 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4541700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1252700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1706000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-231800</v>
       </c>
-      <c r="G102" s="3">
-        <v>-2485300</v>
-      </c>
       <c r="H102" s="3">
+        <v>-2418700</v>
+      </c>
+      <c r="I102" s="3">
         <v>5652100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-886000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>219900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-824200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1222800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>412900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>856800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2840500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1781000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-637000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4380700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,6 +6228,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
